--- a/신고신저가_20260830.xlsx
+++ b/신고신저가_20260830.xlsx
@@ -6251,43 +6251,43 @@
         <v>2.8</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>27.4</v>
+        <v>32.8</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>17.9</v>
+        <v>24.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-13.7</v>
+        <v>-11.9</v>
       </c>
       <c r="O30" t="n">
         <v>2</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-15.3</v>
+        <v>-14.4</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>-14.2</v>
+        <v>-13.5</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>-3.7</v>
+        <v>-1.2</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
@@ -6319,46 +6319,46 @@
         <v>-2.8</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-4.2</v>
+        <v>-3.4</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>22.9</v>
+        <v>26.2</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>27.1</v>
+        <v>32.1</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-14.1</v>
+        <v>-12.8</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-18.6</v>
+        <v>-17.8</v>
       </c>
       <c r="Q31" t="n">
         <v>2</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>-23.2</v>
+        <v>-23.6</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
       </c>
       <c r="T31" s="6" t="n">
-        <v>-4.1</v>
+        <v>-2</v>
       </c>
       <c r="U31" t="n">
         <v>2</v>
@@ -6408,7 +6408,7 @@
         <v>18.9</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>-9.300000000000001</v>
